--- a/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/file_inventory.xlsx
+++ b/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/file_inventory.xlsx
@@ -176,7 +176,7 @@
     <t>個別銘柄の時点別ファクター値、リターン、時価総額、通貨、属性</t>
   </si>
   <si>
-    <t>FAコード、名称、グループ、方向、統合方法</t>
+    <t>FAコード、名称、グループ、方向、統合方法、差分・移動平均乖離の生成設定</t>
   </si>
   <si>
     <t>前処理、モデル、評価、出力可否</t>
@@ -242,10 +242,10 @@
     <t>中立化後ファクタースコアについて、過去RankICとファクター相関からグループ内ウェイトを推定し、グループ間は等ウェイトします。時点tのウェイトにはt-1以前だけを使用します。</t>
   </si>
   <si>
-    <t>各ファクターをLinear・Piecewise・Quadratic・Combined RidgeからOOSで選択し、予測値を0-1スコアへ変換後、グループ内・グループ間を等ウェイトします。</t>
-  </si>
-  <si>
-    <t>選択済み単一ファクターモデル、Excelで指定したグループ統合方法、グループ間OOF Ridgeを順に適用したフルモデルです。</t>
+    <t>設定された原系列・差分・移動平均乖離等をそれぞれ1ファクターとして扱い、Linear・Piecewise・Quadratic・Combined RidgeからOOSで選択します。予測値を0-1スコアへ変換後、グループ内・グループ間を等ウェイトします。</t>
+  </si>
+  <si>
+    <t>原系列と設定済み派生ファクターの選択済み単一ファクターモデル、Excelで指定したグループ統合方法、グループ間OOF Ridgeを順に適用したフルモデルです。</t>
   </si>
   <si>
     <t>個別銘柄リターンと単一ファクターの散布図・候補回帰線</t>
